--- a/labs/lab-01-compare-generative-agentic-and-agent-ai-for-finance/ai-type-use-case-map-starter.xlsx
+++ b/labs/lab-01-compare-generative-agentic-and-agent-ai-for-finance/ai-type-use-case-map-starter.xlsx
@@ -25,7 +25,7 @@
     <t>Course</t>
   </si>
   <si>
-    <t>Generative AI for Finance and Fintech (TGS-2026065050)</t>
+    <t>Microsoft Copilot for Finance (TGS-2026065050)</t>
   </si>
   <si>
     <t>TSC mapping</t>
